--- a/reports/hazop_vision_system_27.xlsx
+++ b/reports/hazop_vision_system_27.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -480,7 +480,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Model reading: This P&amp;ID illustrates the Export Booster Compressor (27-KA50) system, detailing its suction and discharge lines, anti-surge control, and associated instrumentation. It includes connections to a wet gas scrubber, cold vent, and seal gas system, with various pressure, temperature, and flow monitoring points.</t>
+          <t>Model reading: This P&amp;ID depicts the Export Booster Compressor (27-KA50) and its associated suction and discharge piping, including anti-surge control, safety systems, and instrumentation. The diagram details control strategies for the compressor, such as pressure control via discharge throttling or compressor speed, and includes notes on specific operational procedures and interlocks. It outlines connections to wet gas scrubbers, cold vents, and an aftercooler.</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>No Flow / Surge</t>
+          <t>Low Flow</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The anti-surge control system relies on a single control valve (27-XV4814) and its positioner (27-XY4814). A failure of this valve or its control logic, such as failing to open, could lead to compressor surge or damage, especially given its crucial role described in Note 12.</t>
+          <t>The anti-surge valve (implied by note 12 involving control logic) is designed to operate as a control valve with a minimum opening restriction (5%). If this minimum opening is too restrictive or the control logic fails, it could lead to an insufficient flow condition or surge.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27-XY4814, 27-XV4814, 27-ZS4814, 27-ZL4814, 27-HS4814, ANTI-SURGE CONTROL, 27-4503PV, 27-4504PV</t>
+          <t>ANTI-SURGE CONTROL, 27-4453PV</t>
         </is>
       </c>
     </row>
@@ -537,12 +537,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>A single pressure safety valve (27-PSV4809) protects the compressor discharge from overpressure due to a blocked outlet. Its correct functioning is critical, and its failure to open could lead to equipment rupture. A key interlock (SI-4208) is associated with the system, implying operational constraints to prevent overpressure.</t>
+          <t>The spill-off valve 27-PV4803 is specifically designated for compressor start-up (Note 7). A failure to open during start-up could lead to high pressure or surge, while a failure to close after start-up could lead to continuous bypass and reduced compressor efficiency or low discharge pressure.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27-PSV4809, SI-4208, 43-4505VF, BS200 ED200, AS200, 27-4453PV</t>
+          <t>27-PV4803, 27-KA50</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>More Of (Liquid) / No Flow</t>
+          <t>Incorrect Operation</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The compressor suction line, coming from a wet gas scrubber, has multiple low points and drain connections (e.g., Note 13, Note 5). If the upstream scrubber malfunctions or these drains become blocked, there is a risk of liquid accumulation or slugging entering the compressor, which can cause severe damage or surge.</t>
+          <t>A key interlock (SI 4208, Note 16) prevents 27-4453PV from being closed while 27-4452PV is open. A failure of this interlock, or bypassing it, could lead to an unintended valve configuration resulting in equipment damage or an unsafe operating condition (e.g., dead-heading the compressor).</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>W-HO24-P-*-E-002, 27-FE4801, 27-PI4801, 27-PT4823, NOTE 13, NOTE 5, NOTE 9</t>
+          <t>SI 4208, 27-4452PV, 27-4453PV</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Less Flow / More Flow / High Pressure</t>
+          <t>Loss of Control</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The control valve (27-FV4811) to the HP cold vent system has a travel stop to limit flow rate, as specified in Note 19. A failure of this valve to open, or an incorrect setting of the travel stop, could lead to insufficient venting and potential overpressure, or conversely, excessive venting if it fails fully open.</t>
+          <t>Pressure upstream of the compressor can be controlled by two different methods: discharge throttling using 27-PIC4825A/B or varying compressor speed via 27-PIC4825C (Note 22). This dual control strategy introduces complexity which needs careful review for potential conflicts or failures leading to loss of control.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27-FV4811, 27-XV4811, 27-HSL4811, 27-XY4811, TO HP COLD VENT W-HO43-P-*-F-001, NOTE 19, NOTE 10</t>
+          <t>27-PIC4825A, 27-PIC4825B, 27-PIC4825C, 27-KA50</t>
         </is>
       </c>
     </row>
@@ -592,17 +592,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>No Flow / More Flow / Reverse Flow</t>
+          <t>Less Flow</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The spill-off valve (27-PV4803) is designated specifically for compressor start-up (Note 7). A failure of this valve to open or close correctly during the start-up sequence could lead to unstable operation, surge, or an inability to achieve desired process conditions, impacting safe start-up procedures.</t>
+          <t>The bolt catcher must be removed one month after compressor start-up (Note 20). Failure to follow this temporary operational instruction could lead to reduced flow, increased pressure drop, or potential damage to downstream equipment due to foreign material if the catcher breaks apart.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27-PV4803, 27-PIC4803, 27-PT4803, 27-PY4803, 27-4542PV, NOTE 7</t>
+          <t>27-KA50</t>
         </is>
       </c>
     </row>
@@ -612,17 +612,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Inaccurate Measurement / High Pressure / Low Pressure</t>
+          <t>High Pressure</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Multiple pressure transmitters (e.g., 27-PDI4812, 27-PT4805, 27-PT4825) and controllers (27-PIC4825A/B/C) are used for monitoring compressor pressure conditions. While providing detailed feedback, potential discrepancies between redundant sensors or common mode failures could lead to incorrect control actions or misleading operational data, affecting compressor protection schemes (e.g., Note 2 on PALL).</t>
+          <t>Low pressure permissives are required for opening drain valves 27-XV4826 and 27-XV4828 (Notes 17, 18). If these permissives (likely sensed by 27-PT4807) fail or are overridden, it could lead to the opening of drain valves under high pressure, posing a safety risk.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27-PDI4812, 27-PI4805, 27-PT4805, 27-PIC4825A, 27-PIC4825B, 27-PIC4825C, 27-PT4825, NOTE 2</t>
+          <t>27-XV4826, 27-XV4828, 27-PT4807</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -672,313 +672,313 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>27-XY4814</t>
+          <t>ANTI-SURGE CONTROL</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>bekreftet i uttrekket</t>
+          <t>ukjent format / mulig hallusinasjon</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>observation 1: No Flow / Surge</t>
+          <t>observation 1: Low Flow</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>27-XV4814</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>observation 1: No Flow / Surge</t>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>27-4453PV</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>observation 1: Low Flow</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>27-ZS4814</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>observation 1: No Flow / Surge</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>27-PV4803</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: High Pressure</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>27-ZL4814</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>observation 1: No Flow / Surge</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>27-KA50</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>observation 2: High Pressure</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>27-HS4814</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>observation 1: No Flow / Surge</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>SI 4208</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>observation 3: Incorrect Operation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ANTI-SURGE CONTROL</t>
+          <t>27-4452PV</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>ukjent format / mulig hallusinasjon</t>
+          <t>bekreftet i uttrekket</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>observation 1: No Flow / Surge</t>
+          <t>observation 3: Incorrect Operation</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>27-4503PV</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>observation 1: No Flow / Surge</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>27-4453PV</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>observation 3: Incorrect Operation</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>27-4504PV</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>observation 1: No Flow / Surge</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>27-PIC4825A</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>observation 4: Loss of Control</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>27-PSV4809</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>observation 2: High Pressure</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>27-PIC4825B</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>observation 4: Loss of Control</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>SI-4208</t>
+          <t>27-PIC4825C</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>ukjent format / mulig hallusinasjon</t>
+          <t>bekreftet i uttrekket</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>observation 2: High Pressure</t>
+          <t>observation 4: Loss of Control</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>43-4505VF</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>observation 2: High Pressure</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>27-KA50</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>observation 4: Loss of Control</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>BS200 ED200</t>
+          <t>27-KA50</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>ukjent format / mulig hallusinasjon</t>
+          <t>bekreftet i uttrekket</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>observation 2: High Pressure</t>
+          <t>observation 5: Less Flow</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>AS200</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>observation 2: High Pressure</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>27-XV4826</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>observation 6: High Pressure</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>27-4453PV</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>observation 2: High Pressure</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>27-XV4828</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>observation 6: High Pressure</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>W-HO24-P-*-E-002</t>
+          <t>27-PT4807</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>ukjent format / mulig hallusinasjon</t>
+          <t>bekreftet i uttrekket</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>observation 3: More Of (Liquid) / No Flow</t>
+          <t>observation 6: High Pressure</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>27-FE4801</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>observation 3: More Of (Liquid) / No Flow</t>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>27-KA50</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Reciprocating Compressor</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>27-PI4801</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>observation 3: More Of (Liquid) / No Flow</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>27-PT4803</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure Transmitter</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>27-PT4823</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>observation 3: More Of (Liquid) / No Flow</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>27-PV4803</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Control Valve</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NOTE 13</t>
+          <t>27-PI4801</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -988,65 +988,65 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>observation 3: More Of (Liquid) / No Flow</t>
+          <t>symbol-only candidate: Pressure Indicator</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>NOTE 5</t>
+          <t>27-PSV4809</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ukjent format / mulig hallusinasjon</t>
+          <t>bekreftet i uttrekket</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>observation 3: More Of (Liquid) / No Flow</t>
+          <t>symbol-only candidate: Pressure Safety Valve</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>NOTE 9</t>
+          <t>27-PSV4810</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>ukjent format / mulig hallusinasjon</t>
+          <t>bekreftet i uttrekket</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>observation 3: More Of (Liquid) / No Flow</t>
+          <t>symbol-only candidate: Pressure Safety Valve</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>27-FV4811</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>observation 4: Less Flow / More Flow / High Pressure</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>27-TT4806</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Temperature Transmitter</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>27-XV4811</t>
+          <t>SI 4208</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -1056,592 +1056,65 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>observation 4: Less Flow / More Flow / High Pressure</t>
+          <t>symbol-only candidate: Safety Interlock</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>27-HSL4811</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>observation 4: Less Flow / More Flow / High Pressure</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>27-PIC4825A</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure Indicating Controller</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>27-XY4811</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>observation 4: Less Flow / More Flow / High Pressure</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>27-XV4826</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Manual Valve</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>TO HP COLD VENT W-HO43-P-*-F-001</t>
+          <t>27-FO4827</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>ukjent format / mulig hallusinasjon</t>
+          <t>bekreftet i uttrekket</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>observation 4: Less Flow / More Flow / High Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>NOTE 19</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>observation 4: Less Flow / More Flow / High Pressure</t>
+          <t>symbol-only candidate: Flow Orifice</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>NOTE 10</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>observation 4: Less Flow / More Flow / High Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>27-PV4803</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>observation 5: No Flow / More Flow / Reverse Flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>27-PIC4803</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>observation 5: No Flow / More Flow / Reverse Flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>27-PT4803</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>observation 5: No Flow / More Flow / Reverse Flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>27-PY4803</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>observation 5: No Flow / More Flow / Reverse Flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>27-4542PV</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>observation 5: No Flow / More Flow / Reverse Flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>NOTE 7</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>ukjent format / mulig hallusinasjon</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>observation 5: No Flow / More Flow / Reverse Flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>27-PDI4812</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>observation 6: Inaccurate Measurement / High Pressure / Low Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>27-PI4805</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>observation 6: Inaccurate Measurement / High Pressure / Low Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>27-PT4805</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>observation 6: Inaccurate Measurement / High Pressure / Low Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>27-PIC4825A</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>observation 6: Inaccurate Measurement / High Pressure / Low Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>27-PIC4825B</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>observation 6: Inaccurate Measurement / High Pressure / Low Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>27-PIC4825C</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>observation 6: Inaccurate Measurement / High Pressure / Low Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>27-PT4825</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>observation 6: Inaccurate Measurement / High Pressure / Low Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>NOTE 2</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>ukjent format / mulig hallusinasjon</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>observation 6: Inaccurate Measurement / High Pressure / Low Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>27-KA50</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Compressor</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>27-PV4803</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Automatic Control Valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>27-PT4803</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Pressure Transmitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>27-PIC4803</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Pressure Indicating Controller</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>27-PSV4809</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Pressure Safety Valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>SI-4208</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>ukjent format / mulig hallusinasjon</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Safety Interlock</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>27-XV4814</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Automatic Valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>27-XY4814</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Valve Positioner</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>27-ZS4814</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Position Switch</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>27-PDI4812</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Pressure Differential Indicator</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>27-TT4806</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Temperature Transmitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>27-FV4811</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Flow Control Valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>27-FE4801</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Flow Element (Orifice Plate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>27-FT4801</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Flow Transmitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>27-4542PV</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Globe Valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Totals: 35 verified · 0 verified (normalised) · 12 new candidates · 10 unknown format</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Totals: 22 verified · 0 verified (normalised) · 3 new candidates · 1 unknown format</t>
         </is>
       </c>
     </row>

--- a/reports/hazop_vision_system_27.xlsx
+++ b/reports/hazop_vision_system_27.xlsx
@@ -39,7 +39,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,17 +53,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -94,6 +99,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Model reading: This P&amp;ID depicts the Export Booster Compressor (27-KA50) and its associated suction and discharge piping, including anti-surge control, safety systems, and instrumentation. The diagram details control strategies for the compressor, such as pressure control via discharge throttling or compressor speed, and includes notes on specific operational procedures and interlocks. It outlines connections to wet gas scrubbers, cold vents, and an aftercooler.</t>
+          <t>Model reading: The drawing details the process and instrumentation for an Export Booster Compressor (27-KA50) system, including its suction and discharge piping, anti-surge control, connections to wet gas coolers, cold vents, and seal gas. It highlights various pressure, temperature, level, and flow instrumentation, as well as critical safety interlocks and pressure relief devices to ensure safe and efficient operation.</t>
         </is>
       </c>
     </row>
@@ -512,17 +520,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Low Flow</t>
+          <t>High pressure</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The anti-surge valve (implied by note 12 involving control logic) is designed to operate as a control valve with a minimum opening restriction (5%). If this minimum opening is too restrictive or the control logic fails, it could lead to an insufficient flow condition or surge.</t>
+          <t>Multiple pressure safety valves (PSVs) are installed on the compressor discharge, with an interlock system, to protect against overpressure. The basis for setting is a high pressure (150 barg) for a blocked outlet scenario.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ANTI-SURGE CONTROL, 27-4453PV</t>
+          <t>27-KA50, 27-PSV4809, 27-PSV4810, 27-4452PV, 27-4453PV, SI4207, SI4206, 27-PI4807, NOTE 14, NOTE 16</t>
         </is>
       </c>
     </row>
@@ -532,17 +540,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>High Pressure</t>
+          <t>Low Flow / Surge</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The spill-off valve 27-PV4803 is specifically designated for compressor start-up (Note 7). A failure to open during start-up could lead to high pressure or surge, while a failure to close after start-up could lead to continuous bypass and reduced compressor efficiency or low discharge pressure.</t>
+          <t>An anti-surge control system is implemented with dedicated flow and pressure instruments to protect the compressor from surge. The system includes specific logic and minimum valve opening restrictions (5%) for operation.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27-PV4803, 27-KA50</t>
+          <t>27-KA50, ANTI-SURGE CONTROL, 27-FC4811, 27-FY4811, 27-PIC4825A, 27-PIC4825B, 27-PIC4825C, 27-PT4825, NOTE 12, NOTE 21, NOTE 22</t>
         </is>
       </c>
     </row>
@@ -552,17 +560,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Incorrect Operation</t>
+          <t>Reverse Flow</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>A key interlock (SI 4208, Note 16) prevents 27-4453PV from being closed while 27-4452PV is open. A failure of this interlock, or bypassing it, could lead to an unintended valve configuration resulting in equipment damage or an unsafe operating condition (e.g., dead-heading the compressor).</t>
+          <t>A 'NON SLAM CHECK VALVE' is specified to be mounted on a high point at the compressor discharge (Note 1), which is crucial for preventing reverse flow. Failure of this check valve could lead to reverse flow conditions.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>SI 4208, 27-4452PV, 27-4453PV</t>
+          <t>27-KA50, NOTE 1</t>
         </is>
       </c>
     </row>
@@ -572,17 +580,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Loss of Control</t>
+          <t>High Flow / Low Flow</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Pressure upstream of the compressor can be controlled by two different methods: discharge throttling using 27-PIC4825A/B or varying compressor speed via 27-PIC4825C (Note 22). This dual control strategy introduces complexity which needs careful review for potential conflicts or failures leading to loss of control.</t>
+          <t>A dedicated control valve system with a travel stop (Note 19) is used to limit flow rate to the HP cold vent system. Malfunction could lead to excessive venting or insufficient capacity for gas release.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27-PIC4825A, 27-PIC4825B, 27-PIC4825C, 27-KA50</t>
+          <t>27-XY4814, 27-XV4814, 27-ZS4814, 27-ZL4814, NOTE 19, TO HP COLD VENT</t>
         </is>
       </c>
     </row>
@@ -592,17 +600,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Less Flow</t>
+          <t>Contamination / Two-Phase Flow</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The bolt catcher must be removed one month after compressor start-up (Note 20). Failure to follow this temporary operational instruction could lead to reduced flow, increased pressure drop, or potential damage to downstream equipment due to foreign material if the catcher breaks apart.</t>
+          <t>The compressor takes suction from a 'WET GAS SCRUBBER'. This implies a potential for liquid carry-over or slugging, which could cause mechanical damage or process upsets to the compressor (27-KA50).</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27-KA50</t>
+          <t>FROM WET GAS SCRUBBER, W-H024-P-*-E-002, 27-KA50</t>
         </is>
       </c>
     </row>
@@ -612,17 +620,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>High Pressure</t>
+          <t>Maloperation / Interlock Failure</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Low pressure permissives are required for opening drain valves 27-XV4826 and 27-XV4828 (Notes 17, 18). If these permissives (likely sensed by 27-PT4807) fail or are overridden, it could lead to the opening of drain valves under high pressure, posing a safety risk.</t>
+          <t>Drain valves (27-XV4826, 27-XV4828) are interlocked with low-pressure permissives (33 barg), which is a safety feature. Failure of this interlock or associated instruments could prevent necessary draining or cause inadvertent draining.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27-XV4826, 27-XV4828, 27-PT4807</t>
+          <t>27-XV4826, 27-XV4828, 27-HS4826, 27-HS4828, 27-XY4826, 27-XY4828, 27-ZS4826, 27-ZS4828, 27-ZL4826, 27-ZL4828, NOTE 17, NOTE 18</t>
         </is>
       </c>
     </row>
@@ -644,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -672,449 +680,993 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>ANTI-SURGE CONTROL</t>
+          <t>27-KA50</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>ukjent format / mulig hallusinasjon</t>
+          <t>bekreftet i uttrekket</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>observation 1: Low Flow</t>
+          <t>observation 1: High pressure</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>27-4453PV</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>observation 1: Low Flow</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>27-PSV4809</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>observation 1: High pressure</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>27-PV4803</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>observation 2: High Pressure</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>27-PSV4810</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>observation 1: High pressure</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>27-KA50</t>
+          <t>27-4452PV</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>bekreftet i uttrekket</t>
+          <t>NY KANDIDAT - sjekk tegning</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>observation 2: High Pressure</t>
+          <t>observation 1: High pressure</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>SI 4208</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>observation 3: Incorrect Operation</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>27-4453PV</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>observation 1: High pressure</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>27-4452PV</t>
+          <t>SI4207</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>bekreftet i uttrekket</t>
+          <t>NY KANDIDAT - sjekk tegning</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>observation 3: Incorrect Operation</t>
+          <t>observation 1: High pressure</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>27-4453PV</t>
+          <t>SI4206</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>bekreftet i uttrekket</t>
+          <t>NY KANDIDAT - sjekk tegning</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>observation 3: Incorrect Operation</t>
+          <t>observation 1: High pressure</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>27-PIC4825A</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>observation 4: Loss of Control</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>27-PI4807</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>observation 1: High pressure</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>27-PIC4825B</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>observation 4: Loss of Control</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>NOTE 14</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>observation 1: High pressure</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>27-PIC4825C</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>observation 4: Loss of Control</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>NOTE 16</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>observation 1: High pressure</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>27-KA50</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>observation 4: Loss of Control</t>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>27-KA50</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>observation 5: Less Flow</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>ANTI-SURGE CONTROL</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>27-XV4826</t>
+          <t>27-FC4811</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>bekreftet i uttrekket</t>
+          <t>NY KANDIDAT - sjekk tegning</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>observation 6: High Pressure</t>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>27-XV4828</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>observation 6: High Pressure</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>27-FY4811</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>27-PT4807</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>observation 6: High Pressure</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>27-PIC4825A</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>27-KA50</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Reciprocating Compressor</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>27-PIC4825B</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>27-PT4803</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Pressure Transmitter</t>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>27-PIC4825C</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>27-PV4803</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Control Valve</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>27-PT4825</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>27-PI4801</t>
+          <t>NOTE 12</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>NY KANDIDAT - sjekk tegning</t>
+          <t>ukjent format / mulig hallusinasjon</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>symbol-only candidate: Pressure Indicator</t>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>27-PSV4809</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Pressure Safety Valve</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>NOTE 21</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>27-PSV4810</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Pressure Safety Valve</t>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>NOTE 22</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>observation 2: Low Flow / Surge</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>27-TT4806</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Temperature Transmitter</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>27-KA50</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>observation 3: Reverse Flow</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>SI 4208</t>
+          <t>NOTE 1</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>observation 3: Reverse Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>27-XY4814</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>observation 4: High Flow / Low Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>27-XV4814</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>observation 4: High Flow / Low Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>27-ZS4814</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>observation 4: High Flow / Low Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>27-ZL4814</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>observation 4: High Flow / Low Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>NOTE 19</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>observation 4: High Flow / Low Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>TO HP COLD VENT</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>observation 4: High Flow / Low Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>FROM WET GAS SCRUBBER</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>observation 5: Contamination / Two-Phase Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>W-H024-P-*-E-002</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>observation 5: Contamination / Two-Phase Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>27-KA50</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>observation 5: Contamination / Two-Phase Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>27-XV4826</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>27-XV4828</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>27-HS4826</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>27-HS4828</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>27-XY4826</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>27-XY4828</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>27-ZS4826</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>27-ZS4828</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>27-ZL4826</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>27-ZL4828</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>NOTE 17</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>NOTE 18</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>ukjent format / mulig hallusinasjon</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>observation 6: Maloperation / Interlock Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>27-PT4803</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure Transmitter</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>27-PIC4803</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure Indicator Controller</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>27-PV4803</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Control Valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>27-HS4814</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Hand Switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>27-PSV4809</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure Safety Valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>27-FY4811</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>bekreftet ((type, nr)-match)</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Flow Transmitter</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>27-FC4811</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
           <t>NY KANDIDAT - sjekk tegning</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Flow Controller / Control Valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>SI4207</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>symbol-only candidate: Safety Interlock</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>27-PDI4812</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure Differential Indicator</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>27-PI4805</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure Indicator</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>27-TT4806</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Temperature Transmitter</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>27-PIC4825A</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Pressure Indicating Controller</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Pressure Indicator Controller</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>27-XV4826</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Manual Valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>27-FO4827</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>bekreftet i uttrekket</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>symbol-only candidate: Flow Orifice</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Totals: 22 verified · 0 verified (normalised) · 3 new candidates · 1 unknown format</t>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>bekreftet i uttrekket</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Control Valve</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>27-FO4811</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>NY KANDIDAT - sjekk tegning</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>symbol-only candidate: Orifice Plate</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Totals: 36 verified · 2 verified (normalised) · 7 new candidates · 13 unknown format</t>
         </is>
       </c>
     </row>
